--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
@@ -768,7 +768,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
@@ -778,7 +778,7 @@
         <v>1.25</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>3</v>
@@ -827,17 +827,17 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1.5</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>5</v>
@@ -886,17 +886,17 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1.75</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>7</v>
@@ -945,17 +945,17 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>9</v>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2.25</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>11</v>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2.5</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>13</v>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>410</v>
+        <v>195</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2.75</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>15</v>
@@ -1270,17 +1270,17 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Skill_Level_Sum</t>
+          <t>Skill_Node_Count</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>공용 스킬 레벨 합</t>
+          <t>활성화한 공용 스킬 노드 수 (훈장 시작점 제외)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>필요한 합계</t>
+          <t>필요한 노드 수</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>판 시작 때 쥐 마릿수</t>
+          <t>판 시작 때 쥐 기본 마릿수 (무작위 등급). 공용 스킬 "시작 쥐" 노드가 등급 지정해서 더함</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>고를 수 있는 시작 층 상한 (최고 도달 층을 넘지 못함)</t>
+          <t>(안 씀) 시작 층은 공용 스킬 "스테이지 스킵" 노드 합으로</t>
         </is>
       </c>
     </row>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>1.25</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>3</v>
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1.5</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>5</v>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1.75</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>7</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>9</v>
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2.25</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>11</v>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2.5</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>13</v>
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2.75</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>15</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>활성화한 공용 스킬 노드 수 (훈장 시작점 제외)</t>
+          <t>지금 훈장 트리에서 활성화한 공용 스킬 노드 수 (훈장 시작점 제외). 승급하려면 지금 트리를 이만큼 찍어야 함</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -778,7 +778,7 @@
         <v>1.25</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>3</v>
@@ -837,7 +837,7 @@
         <v>1.5</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>5</v>
@@ -896,7 +896,7 @@
         <v>1.75</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>7</v>
@@ -955,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>9</v>
@@ -1014,7 +1014,7 @@
         <v>2.25</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>11</v>
@@ -1073,7 +1073,7 @@
         <v>2.5</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>13</v>
@@ -1132,7 +1132,7 @@
         <v>2.75</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>15</v>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>850</v>
+        <v>940</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1900</v>
+        <v>2460</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>4200</v>
+        <v>8650</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -768,11 +768,11 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1.25</v>
@@ -827,11 +827,11 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1.5</v>
@@ -886,11 +886,11 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1.75</v>
@@ -945,11 +945,11 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>2</v>
@@ -1004,11 +1004,11 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>2.25</v>
@@ -1063,11 +1063,11 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>2.5</v>
@@ -1122,11 +1122,11 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Skill_Node_Count</t>
+          <t>Skill_Tree_Complete</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>2.75</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1281,6 +1281,23 @@
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>필요한 노드 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>지금 훈장까지의 공용 스킬 트리 노드를 전부 활성화 (훈장 시작점 제외). 개수는 트리에서 자동 계산</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>- (안 씀, 0)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>940</v>
+        <v>860</v>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2460</v>
+        <v>2690</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>8650</v>
+        <v>11020</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -456,65 +456,70 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>티어 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>연구자료 비용</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>조건1 타입</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>조건1 값</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>조건2 타입</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>조건2 값</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>조건3 타입</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>조건3 값</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>윗등급 탄생 배율</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>시작 마릿수</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>시작 층 상한</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>배지 에셋</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>쥐 공격력 배율</t>
         </is>
@@ -533,65 +538,70 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>tier_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>research_cost</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>cond1_type</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>cond1_value</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>cond2_type</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>cond2_value</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>cond3_type</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>cond3_value</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>birth_grade_k</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>start_rat_count</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>start_floor_cap</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>badge_asset</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>rat_atk_mul</t>
         </is>
@@ -610,65 +620,70 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -683,53 +698,56 @@
           <t>실험체</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>4100001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>🐭</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_1</t>
         </is>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -742,53 +760,56 @@
           <t>치즈 도둑</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>4100002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>🧀</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_2</t>
         </is>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -801,53 +822,56 @@
           <t>하수구 정찰병</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>4100003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>🔦</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="O6" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_3</t>
         </is>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -860,53 +884,56 @@
           <t>탈출 설계자</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>4100004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>🗝️</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>1.75</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="O7" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_4</t>
         </is>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="P7" s="1" t="n">
         <v>1.75</v>
       </c>
     </row>
@@ -919,53 +946,56 @@
           <t>연구소 브로커</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>4100005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>📋</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>430</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_5</t>
         </is>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="P8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -978,53 +1008,56 @@
           <t>반란 지휘관</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>4100006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>🎖️</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>860</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>2.25</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="O9" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_6</t>
         </is>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -1037,53 +1070,56 @@
           <t>쥐들의 왕</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>4100007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>👑</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="E10" s="1" t="n">
         <v>2690</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="M10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="N10" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_7</t>
         </is>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="P10" s="1" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -1096,53 +1132,56 @@
           <t>전설의 탈옥왕</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>4100008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>🌌</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="E11" s="1" t="n">
         <v>11020</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Max_Floor</t>
         </is>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Shard_Level_Sum</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Skill_Tree_Complete</t>
         </is>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <v>2.75</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="N11" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>Rogue/rk_8</t>
         </is>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="P11" s="1" t="n">
         <v>2.75</v>
       </c>
     </row>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -524,6 +524,16 @@
           <t>쥐 공격력 배율</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>조건4 타입</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>조건4 값</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -606,6 +616,16 @@
           <t>rat_atk_mul</t>
         </is>
       </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>cond4_type</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>cond4_value</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -630,60 +650,70 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1183,6 +1213,566 @@
       </c>
       <c r="P11" s="1" t="n">
         <v>2.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>지하 제국 총독</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4100009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>🏰</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>72800000</v>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_9</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>초월 실험체</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4100010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>🧬</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>216800000</v>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_10</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>연구소 점령자</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4100011</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>🚩</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>648000000</v>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>310</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_11</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>도시의 그림자</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4100012</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>🌃</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1932000000</v>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_12</t>
+        </is>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>쥐 공화국 의장</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>4100013</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>⚖️</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>5760000000</v>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_13</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>행성 탈출자</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>4100014</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>🚀</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>17200000000</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_14</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>은하 방랑자</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>4100015</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>🌌</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>51200000000</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Max_Floor</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>690</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_15</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>찍찍!! 신화</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>4100016</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>👑</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>136800000000</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Boss_Clear</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Shard_Level_Sum</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>810</v>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>Rogue/rk_16</t>
+        </is>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Skill_Tree_Complete</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1196,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1337,6 +1927,40 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>- (안 씀, 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Dex_Count</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>도감에서 만난 친구(쥐 종) 수 (2026-10-19)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>필요한 종 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Boss_Clear</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>이 층까지 클리어 (마지막 보스 처치 = 100)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>클리어해야 하는 층</t>
         </is>
       </c>
     </row>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tier" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cond_Type" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>430</v>
+        <v>560</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>860</v>
+        <v>770</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2690</v>
+        <v>2420</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>11020</v>
+        <v>9920</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>72800000</v>
+        <v>42000</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>216800000</v>
+        <v>87000</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>648000000</v>
+        <v>328000</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>1932000000</v>
+        <v>742000</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>5760000000</v>
+        <v>1872000</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>17200000000</v>
+        <v>3299000</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>51200000000</v>
+        <v>4945000</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>136800000000</v>
+        <v>11154000</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>260</v>
+        <v>160</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>560</v>
+        <v>280</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>770</v>
+        <v>470</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2420</v>
+        <v>1170</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>9920</v>
+        <v>2900</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>690</v>
+        <v>600</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>810</v>
+        <v>690</v>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1170</v>
+        <v>1030</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2900</v>
+        <v>4200</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="I7" s="1" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>280</v>
+        <v>720</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>410</v>
+        <v>1700</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1030</v>
+        <v>4210</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>4200</v>
+        <v>21420</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>42000</v>
+        <v>33000</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>87000</v>
+        <v>55000</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>328000</v>
+        <v>197000</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>742000</v>
+        <v>450000</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1872000</v>
+        <v>1271000</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>3299000</v>
+        <v>1904000</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>4945000</v>
+        <v>2855000</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -1723,15 +1723,15 @@
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>11154000</v>
+        <v>4788000</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>Boss_Clear</t>
+          <t>Max_Floor</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>690</v>
+        <v>495</v>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="I8" s="1" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="I9" s="1" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>4210</v>
+        <v>4070</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>21420</v>
+        <v>17750</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="I11" s="1" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>33000</v>
+        <v>27000</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="I12" s="1" t="n">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>55000</v>
+        <v>45000</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I13" s="1" t="n">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>197000</v>
+        <v>165000</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="I14" s="1" t="n">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>450000</v>
+        <v>378000</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="I15" s="1" t="n">
-        <v>335</v>
+        <v>255</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1271000</v>
+        <v>1076000</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="I16" s="1" t="n">
-        <v>370</v>
+        <v>285</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1904000</v>
+        <v>1613000</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I17" s="1" t="n">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2855000</v>
+        <v>2416000</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="I18" s="1" t="n">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>4788000</v>
+        <v>4032000</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="I19" s="1" t="n">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>

--- a/Data_Table/티어 테이블.xlsx
+++ b/Data_Table/티어 테이블.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -534,6 +534,11 @@
           <t>조건4 값</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>승급 배율 (누적)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -626,6 +631,11 @@
           <t>cond4_value</t>
         </is>
       </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>rank_mul</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -714,6 +724,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -780,6 +795,9 @@
       <c r="P4" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -799,7 +817,7 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -841,6 +859,9 @@
       </c>
       <c r="P5" s="1" t="n">
         <v>1.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.115</v>
       </c>
     </row>
     <row r="6">
@@ -861,7 +882,7 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -869,7 +890,7 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
@@ -903,6 +924,9 @@
       </c>
       <c r="P6" s="1" t="n">
         <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.2723</v>
       </c>
     </row>
     <row r="7">
@@ -923,7 +947,7 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
@@ -931,7 +955,7 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
@@ -965,6 +989,9 @@
       </c>
       <c r="P7" s="1" t="n">
         <v>1.75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.4849</v>
       </c>
     </row>
     <row r="8">
@@ -985,7 +1012,7 @@
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -993,7 +1020,7 @@
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
@@ -1027,6 +1054,9 @@
       </c>
       <c r="P8" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.7719</v>
       </c>
     </row>
     <row r="9">
@@ -1047,7 +1077,7 @@
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1700</v>
+        <v>1680</v>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
@@ -1055,7 +1085,7 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
@@ -1089,6 +1119,9 @@
       </c>
       <c r="P9" s="1" t="n">
         <v>2.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.1604</v>
       </c>
     </row>
     <row r="10">
@@ -1109,7 +1142,7 @@
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>4070</v>
+        <v>3740</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1117,7 +1150,7 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -1151,6 +1184,9 @@
       </c>
       <c r="P10" s="1" t="n">
         <v>2.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.6905</v>
       </c>
     </row>
     <row r="11">
@@ -1171,7 +1207,7 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>17750</v>
+        <v>18470</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1179,7 +1215,7 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -1213,6 +1249,9 @@
       </c>
       <c r="P11" s="1" t="n">
         <v>2.75</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4208</v>
       </c>
     </row>
     <row r="12">
@@ -1233,7 +1272,7 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>27000</v>
+        <v>48000</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1280,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -1283,6 +1322,9 @@
       </c>
       <c r="R12" t="n">
         <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.4384</v>
       </c>
     </row>
     <row r="13">
@@ -1303,7 +1345,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>45000</v>
+        <v>77000</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1311,7 +1353,7 @@
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
@@ -1353,6 +1395,9 @@
       </c>
       <c r="R13" t="n">
         <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.8746</v>
       </c>
     </row>
     <row r="14">
@@ -1373,7 +1418,7 @@
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>165000</v>
+        <v>788000</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -1381,7 +1426,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
@@ -1423,6 +1468,9 @@
       </c>
       <c r="R14" t="n">
         <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7.9286</v>
       </c>
     </row>
     <row r="15">
@@ -1443,7 +1491,7 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>378000</v>
+        <v>2595000</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -1451,7 +1499,7 @@
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
@@ -1493,6 +1541,9 @@
       </c>
       <c r="R15" t="n">
         <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10.9075</v>
       </c>
     </row>
     <row r="16">
@@ -1513,7 +1564,7 @@
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1076000</v>
+        <v>11128000</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1521,7 +1572,7 @@
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1563,6 +1614,9 @@
       </c>
       <c r="R16" t="n">
         <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15.2899</v>
       </c>
     </row>
     <row r="17">
@@ -1583,7 +1637,7 @@
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1613000</v>
+        <v>62100000</v>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
@@ -1591,7 +1645,7 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1633,6 +1687,9 @@
       </c>
       <c r="R17" t="n">
         <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>21.8318</v>
       </c>
     </row>
     <row r="18">
@@ -1653,7 +1710,7 @@
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2416000</v>
+        <v>190080000</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -1661,7 +1718,7 @@
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
@@ -1703,6 +1760,9 @@
       </c>
       <c r="R18" t="n">
         <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>31.7419</v>
       </c>
     </row>
     <row r="19">
@@ -1723,7 +1783,7 @@
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>4032000</v>
+        <v>583200000</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
@@ -1731,7 +1791,7 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
@@ -1773,6 +1833,9 @@
       </c>
       <c r="R19" t="n">
         <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>46.978</v>
       </c>
     </row>
   </sheetData>
